--- a/dirigeants.xlsx
+++ b/dirigeants.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Dirigeants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dirigeants'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dirigeants'!$A$1:$J$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,18 +433,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -503,37 +503,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PASCALE</t>
+          <t>FRANÇOIS</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CHARPY-MOORE (CHARPY)</t>
+          <t>DHAUSSY</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Membre du directoire</t>
+          <t>Directeur Général</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>CAISSE D'EPARGNE ET DE PREVOYANCE LOIRE-CENTRE (CELC)</t>
+          <t>CAFPI</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>383952470</t>
+          <t>510302953</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ORLEANS</t>
+          <t>PARIS</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>66.22Z</t>
+          <t>66.19B</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -547,37 +547,37 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SYLVIE</t>
+          <t>JULIEN</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>LOIRE-FABRE (LOIRE-FABRE)</t>
+          <t>LANGLADE</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Membre du directoire</t>
+          <t>Président de SAS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>CAISSE D'EPARGNE ET DE PREVOYANCE LOIRE-CENTRE (CELC)</t>
+          <t>CAFPI</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>383952470</t>
+          <t>510302953</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ORLEANS</t>
+          <t>PARIS</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>66.22Z</t>
+          <t>66.19B</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -589,43 +589,43 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>VINCENT MARTINIEN THIERRY</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>MANSUY</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Membre du directoire</t>
+          <t>Président de SAS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>CAISSE D'EPARGNE ET DE PREVOYANCE LOIRE-CENTRE (CELC)</t>
+          <t>SYF (FINANCE CONSEIL) (FINANCE CONSEIL)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>383952470</t>
+          <t>490122538</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ORLEANS</t>
+          <t>PARIS</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66.22Z</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.financeconseil.fr</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>reclamation@financeconseil.fr</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
@@ -633,51 +633,2131 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>JULIEN RENE</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>NEGRE</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Membre du directoire</t>
+          <t>Directeur Général</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>CAISSE D'EPARGNE ET DE PREVOYANCE LOIRE-CENTRE (CELC)</t>
+          <t>SYF (FINANCE CONSEIL) (FINANCE CONSEIL)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383952470</t>
+          <t>490122538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>ORLEANS</t>
+          <t>PARIS</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66.22Z</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.financeconseil.fr</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>reclamation@financeconseil.fr</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LUDOVIC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>HUZIEUX</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ARTEMIS COURTAGE (MODERATIO)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>512444282</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.artemiscourtage.com</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>confidentialite@artemisambitions.com</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>XAVIER</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>LACOMBE</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ARTEMIS COURTAGE (MODERATIO)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>512444282</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.artemiscourtage.com</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>confidentialite@artemisambitions.com</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MATHIEU</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>PREVOST</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ARTEMIS COURTAGE (MODERATIO)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>512444282</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.artemiscourtage.com</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>confidentialite@artemisambitions.com</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BERNARD ARMAND SIMON</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>DALBIEZ</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Président du conseil de surveillance</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>CENTRE DE CONSEIL ET DE SERVICE -CCS</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>504514555</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>NANTES</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ANTONY JEAN DANIEL</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>PRISSETTE</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PREMIDIRECT</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>421422734</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>GONDREVILLE</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>PREMIDIRECT</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>421422734</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>GONDREVILLE</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ISIDORO JOSE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ALANIS MARCOS</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>GLOBAL EXCHANGE FRANCE CURRENCY SERVICES</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>893717215</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>TREMBLAY-EN-FRANCE</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>DORA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>D'AMBROSIO</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>VALORITY INVESTISSEMENT (VALORITY INVESTISSEMENT IMMOBILIER)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>442404356</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>LYON</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.valority.com</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>serviceclient@valority.com</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MAXIME CLÉMENT</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>LAUREYSSENS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>VALORITY INVESTISSEMENT (VALORITY INVESTISSEMENT IMMOBILIER)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>442404356</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>LYON</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.valority.com</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>serviceclient@valority.com</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CHRISTOPHE MARCEL CLAUDE</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>VERPILLOT</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>VALORITY INVESTISSEMENT (VALORITY INVESTISSEMENT IMMOBILIER)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>442404356</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>LYON</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.valority.com</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>serviceclient@valority.com</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CHRISTOPHE MARCEL CLAUDE</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>VERPILLOT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>VALORITY CREDIT</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>483471157</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>LYON</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.valority.com</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>serviceclient@valority.com</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>VALORITY CREDIT</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>483471157</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>LYON</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.valority.com</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>serviceclient@valority.com</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GUIREC</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>PENHOAT</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>FIDUCIAL CONSEIL EN ABREGE FINANCIAL</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>348168667</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>COURBEVOIE</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>VIANAS</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>UFIFRANCE PATRIMOINE (UFF) (UFF)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>776042210</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>BOIS-COLOMBES</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SYLVAIN</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>MEHARECHE</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Directeur général délégué</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PARTNERS FINANCES (PARTNERS FINANCES)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>404681496</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PARTNERS FINANCES (PARTNERS FINANCES)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>404681496</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PHILIPPE</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>DE VANSSAY DE BLAVOUS</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>MANAGE - IT</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>821013828</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>LE HAVRE</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>NICOLAS</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>PUECH</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>MANAGE - IT</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>821013828</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>LE HAVRE</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MASSOU</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>COHEN</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>CLINIQUE CHAMPS-ELYSEES FRANCE</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>843623349</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TRACY</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SAYAG (COHEN)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>CLINIQUE CHAMPS-ELYSEES FRANCE</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>843623349</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>JEAN-DIDIER</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>AURIOL</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>PLURIFINANCES</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>495235368</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>OBERHAUSBERGEN</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.plurifinances.fr</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>contact@plurifinances.fr</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CELINE</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>FARRUDJA</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>PLURIFINANCES</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>495235368</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>OBERHAUSBERGEN</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.plurifinances.fr</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>contact@plurifinances.fr</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL CURRENCY EXCHANGE FRANCE</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>395175284</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>FRANCOIS</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>CASALONGA</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>SCM LE FLORIDE</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>382457927</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>HYERES</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>MATHIEU</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>COMBES</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>SCM LE FLORIDE</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>382457927</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>HYERES</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ANNE</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>DUMAS DE LA ROQUE</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>SCM LE FLORIDE</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>382457927</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>HYERES</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SANDRA</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>GAUTHIER CHALVIDAN (GAUTHIER)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>SCM LE FLORIDE</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>382457927</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>HYERES</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>JULIEN</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>VACCARO</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>SCM LE FLORIDE</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>382457927</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>HYERES</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>AURELIEN</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>NAUX</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CAP OR NUMISMATIQUE</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>531338572</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>SAINT-FLORENT</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>JULIEN</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>JOUBERT</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>PRIVILEGE COURTAGE</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>824145304</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GUILLAUME YANN</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>VACCON</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>CREDISSIMMO FRANCE</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>811185388</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>ISLE ADAM</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>QUENTIN SYLVAIN</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>CORNEJO</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>RIA FRANCE</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>493473003</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>GENNEVILLIERS</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ARTHUR BRIAC ENDEOL</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>COSTE</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>RIA FRANCE</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>493473003</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>GENNEVILLIERS</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ANDRZEJ</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>KLAWITER</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>SOCIETE DE DIFFUSION DE MAGASIN (SODIMA)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>652013624</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AURELIEN NICOLAS ALAIN RENE</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ANGUILLE</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>CITY AND CO CENTRE LOIRE (CITY AND CO)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>849438866</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>TOURS</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>THOMAS</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>LHOMME</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>CITY AND CO CENTRE LOIRE (CITY AND CO)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>849438866</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>TOURS</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CEDRIC</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>LEBLANC</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>CVL FINANCES (MAMENSUALITE.FR)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>751624701</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>VERQUIGNEUL</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mamensualite.fr</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>serviceclient@mamensualite.fr</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>JEREMIE JONATHAN</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>FHAL</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>G ET F</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>484414743</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>PATRICK</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>THIBERGE</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>MEILLEURTAUX PLACEMENT</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>494162233</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>THOMAS CYRIL VINCENT</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>VANDEVILLE</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Président du conseil de surveillance</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>MEILLEURTAUX PLACEMENT</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>494162233</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ARNAUD</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ERULIN</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Président du conseil d’administration</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>EDENRED FRANCE</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>393365135</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>MONTROUGE</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ILAN</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>OUANOUNOU</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>EDENRED FRANCE</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>393365135</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>MONTROUGE</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>EMMANUEL JEAN</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>DUCASSE</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Président de SAS</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>CONCILIAPRET</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>793504424</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>LYON</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>JEROME CHRISTIAN PAUL</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>MATON</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>CONCILIAPRET</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>793504424</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>LYON</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>66.19B</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>MAGALI VALÉRIE</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>AUGER</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>SCM IMAGERIE MEDICALE GCN</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>413508961</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>SAINT-GREGOIRE</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>ARNAUD GUY ROGER</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>GEFFRAY</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Gérant</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>SCM IMAGERIE MEDICALE GCN</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>413508961</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>SAINT-GREGOIRE</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>66.19A</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>recherche-entreprises.api.gouv.fr (RCS, donnee publique)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
+  <autoFilter ref="A1:J51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>